--- a/Charlotte_Hornets_2025-26_stats.xlsx
+++ b/Charlotte_Hornets_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,40 +479,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Antonio Reeves</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pat Connaughton</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Mason Plumlee</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tre Mann</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>KJ Simpson</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tidjane Salaün</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Liam McNeeley</t>
         </is>
@@ -548,27 +553,30 @@
         <v>10</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>13</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>12</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>25</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>10</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -602,27 +610,30 @@
         <v>14</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -656,16 +667,16 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -674,9 +685,12 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>4</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -710,27 +724,30 @@
         <v>10</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>8</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>8</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -764,20 +781,20 @@
         <v>17</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>9</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -785,6 +802,9 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -818,27 +838,30 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>11</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>16</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -872,27 +895,30 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>17</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>13</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>7</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -926,27 +952,30 @@
         <v>10</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>18</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>8</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -980,20 +1009,20 @@
         <v>10</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>20</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1001,6 +1030,9 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1034,27 +1066,30 @@
         <v>9</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>8</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1088,28 +1123,145 @@
         <v>17</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>11</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>13</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1123,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,40 +1321,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Antonio Reeves</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pat Connaughton</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Mason Plumlee</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tre Mann</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>KJ Simpson</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tidjane Salaün</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Liam McNeeley</t>
         </is>
@@ -1247,18 +1404,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1298,21 +1458,24 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1346,13 +1509,13 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1364,9 +1527,12 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1409,18 +1575,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1454,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1475,6 +1644,9 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1508,27 +1680,30 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1577,12 +1752,15 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1616,19 +1794,19 @@
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1637,6 +1815,9 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1679,18 +1860,21 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1724,27 +1908,30 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,28 +1965,145 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1813,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,40 +2163,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Antonio Reeves</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pat Connaughton</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Mason Plumlee</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tre Mann</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>KJ Simpson</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tidjane Salaün</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Liam McNeeley</t>
         </is>
@@ -1928,27 +2237,30 @@
         <v>11</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>9</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1982,27 +2294,30 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2036,27 +2351,30 @@
         <v>5</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2090,27 +2408,30 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>6</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2144,27 +2465,30 @@
         <v>7</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2198,27 +2522,30 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>9</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2252,27 +2579,30 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2306,27 +2636,30 @@
         <v>11</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2360,27 +2693,30 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>11</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2414,27 +2750,30 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2468,28 +2807,145 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>13</v>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2503,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,40 +3005,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Antonio Reeves</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pat Connaughton</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Mason Plumlee</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tre Mann</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>KJ Simpson</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tidjane Salaün</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Liam McNeeley</t>
         </is>
@@ -2627,18 +3088,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2690,9 +3154,12 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2744,9 +3211,12 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2789,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -2801,6 +3271,9 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2843,10 +3316,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2855,6 +3328,9 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2897,10 +3373,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2909,6 +3385,9 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2945,24 +3424,27 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2999,24 +3481,27 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3059,10 +3544,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3071,6 +3556,9 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3113,18 +3601,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3161,16 +3652,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3179,7 +3670,124 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3193,7 +3801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3215,7 +3823,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.33333333333333</v>
+        <v>22.28571428571428</v>
       </c>
     </row>
     <row r="3">
@@ -3225,7 +3833,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.81818181818182</v>
+        <v>22.07692307692308</v>
       </c>
     </row>
     <row r="4">
@@ -3235,7 +3843,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.63636363636364</v>
+        <v>17.15384615384615</v>
       </c>
     </row>
     <row r="5">
@@ -3245,7 +3853,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.8</v>
+        <v>15.41666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3265,27 +3873,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.81818181818182</v>
+        <v>10.61538461538461</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.909090909090908</v>
+        <v>10.46153846153846</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.818181818181818</v>
+        <v>10.16666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -3295,7 +3903,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.272727272727273</v>
+        <v>8.153846153846153</v>
       </c>
     </row>
     <row r="11">
@@ -3305,17 +3913,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pat Connaughton</t>
+          <t>Antonio Reeves</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.285714285714286</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="13">
@@ -3331,21 +3939,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tidjane Salaün</t>
+          <t>Pat Connaughton</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.142857142857143</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Tidjane Salaün</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.142857142857143</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Mason Plumlee</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0.5</v>
+      <c r="B16" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3359,7 +3977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,7 +3999,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.833333333333334</v>
+        <v>9.857142857142858</v>
       </c>
     </row>
     <row r="3">
@@ -3391,7 +4009,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3401,7 +4019,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.181818181818182</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3421,27 +4039,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.181818181818182</v>
+        <v>3.307692307692307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.818181818181818</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6</v>
+        <v>2.846153846153846</v>
       </c>
     </row>
     <row r="9">
@@ -3451,7 +4069,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.363636363636364</v>
+        <v>1.461538461538461</v>
       </c>
     </row>
     <row r="10">
@@ -3471,7 +4089,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7272727272727273</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3491,7 +4109,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="14">
@@ -3501,7 +4119,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3511,7 +4129,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Antonio Reeves</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3525,7 +4153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3543,21 +4171,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.454545454545454</v>
+        <v>7.142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -3567,7 +4195,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.181818181818182</v>
+        <v>6.923076923076923</v>
       </c>
     </row>
     <row r="5">
@@ -3577,7 +4205,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.818181818181818</v>
+        <v>6.833333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3587,7 +4215,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.363636363636363</v>
+        <v>5.923076923076923</v>
       </c>
     </row>
     <row r="7">
@@ -3607,7 +4235,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.090909090909091</v>
+        <v>3.307692307692307</v>
       </c>
     </row>
     <row r="9">
@@ -3617,27 +4245,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.727272727272727</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3663,7 +4291,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mason Plumlee</t>
+          <t>Antonio Reeves</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3673,10 +4301,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Mason Plumlee</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3691,7 +4329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3709,11 +4347,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.333333333333333</v>
+        <v>3.307692307692307</v>
       </c>
     </row>
     <row r="3">
@@ -3723,17 +4361,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.181818181818182</v>
+        <v>3.153846153846154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.090909090909091</v>
+        <v>3.142857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -3743,63 +4381,63 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.727272727272727</v>
+        <v>1.692307692307692</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sion James</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.545454545454545</v>
+        <v>1.583333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Sion James</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4</v>
+        <v>1.538461538461539</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Antonio Reeves</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KJ Simpson</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pat Connaughton</t>
+          <t>KJ Simpson</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liam McNeeley</t>
+          <t>Pat Connaughton</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3809,27 +4447,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tidjane Salaün</t>
+          <t>Liam McNeeley</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Tidjane Salaün</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3839,10 +4477,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Moussa Diabaté</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Mason Plumlee</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3857,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4118,6 +4766,48 @@
         <v>211</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>134</v>
+      </c>
+      <c r="D13" t="n">
+        <v>147</v>
+      </c>
+      <c r="E13" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>96</v>
+      </c>
+      <c r="D14" t="n">
+        <v>109</v>
+      </c>
+      <c r="E14" t="n">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
